--- a/Output/PowerPoint_Figures/Fig_S1/Fig_S1b_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S1/Fig_S1b_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,126 +418,126 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>32</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>38</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>40</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>43</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>45</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>48</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>51</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>53</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>56</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>59</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>61</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>64</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>66</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>69</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>72</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>74</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>77</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>80</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>82</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>85</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>88</v>
       </c>
-      <c r="AJ1" s="1" t="n">
+      <c r="AJ1" t="n">
         <v>90</v>
       </c>
-      <c r="AK1" s="1" t="n">
+      <c r="AK1" t="n">
         <v>93</v>
       </c>
-      <c r="AL1" s="1" t="n">
+      <c r="AL1" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.20588235294118</v>
+        <v>2.205882352941179</v>
       </c>
       <c r="C2" t="n">
         <v>0.2898550724637691</v>
@@ -659,7 +647,7 @@
       <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -704,7 +692,7 @@
         <v>0.634920634920671</v>
       </c>
       <c r="O3" t="n">
-        <v>2.460317460317425</v>
+        <v>2.460317460317426</v>
       </c>
       <c r="P3" t="n">
         <v>1.666666666666761</v>
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -801,7 +789,7 @@
         <v>0.955882352941163</v>
       </c>
       <c r="H4" t="n">
-        <v>2.205882352941145</v>
+        <v>2.205882352941146</v>
       </c>
       <c r="I4" t="n">
         <v>2.318840579710112</v>
@@ -816,7 +804,7 @@
         <v>0.5970149253731682</v>
       </c>
       <c r="M4" t="n">
-        <v>1.893939393939501</v>
+        <v>1.893939393939502</v>
       </c>
       <c r="N4" t="n">
         <v>0.3676470588234981</v>
@@ -895,7 +883,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -907,7 +895,7 @@
         <v>1.615384615384621</v>
       </c>
       <c r="D5" t="n">
-        <v>1.969696969696941</v>
+        <v>1.969696969696942</v>
       </c>
       <c r="E5" t="n">
         <v>2.058823529411736</v>
@@ -1013,7 +1001,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1022,7 +1010,7 @@
         <v>0.8088235294117639</v>
       </c>
       <c r="C6" t="n">
-        <v>1.842105263157901</v>
+        <v>1.842105263157902</v>
       </c>
       <c r="D6" t="n">
         <v>1.691176470588212</v>
@@ -1097,7 +1085,7 @@
         <v>1.449275362318923</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.893939393939501</v>
+        <v>1.893939393939502</v>
       </c>
       <c r="AC6" t="n">
         <v>0.7352941176471006</v>
@@ -1131,7 +1119,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1245,7 +1233,7 @@
       <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -1329,7 +1317,7 @@
         <v>2.463768115942169</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.818181818181921</v>
+        <v>1.818181818181922</v>
       </c>
       <c r="AC8" t="n">
         <v>0.3623188405797307</v>
@@ -1361,7 +1349,7 @@
       <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -1448,7 +1436,7 @@
         <v>2.132352941176592</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AD9" t="n">
         <v>1.408450704225432</v>
@@ -1466,7 +1454,7 @@
         <v>2.279411764706012</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.46268656716362</v>
+        <v>2.462686567163619</v>
       </c>
       <c r="AJ9" t="n">
         <v>2.307692307691783</v>
@@ -1479,7 +1467,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1593,7 +1581,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
@@ -1672,7 +1660,7 @@
         <v>2.238805970149381</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AB11" t="n">
         <v>0.3623188405797307</v>
@@ -1709,7 +1697,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
@@ -1769,7 +1757,7 @@
         <v>1.571428571428661</v>
       </c>
       <c r="T12" t="n">
-        <v>1.893939393939501</v>
+        <v>1.893939393939502</v>
       </c>
       <c r="U12" t="n">
         <v>1.838235294117752</v>
@@ -1825,7 +1813,7 @@
       <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -1941,7 +1929,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.5.1</t>
         </is>
@@ -2052,14 +2040,14 @@
         <v>2.028985507245916</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.391304347825544</v>
+        <v>2.391304347825543</v>
       </c>
       <c r="AL14" t="n">
         <v>0.2205882352940675</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.5.2</t>
         </is>
@@ -2177,7 +2165,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.5.3</t>
         </is>
@@ -2276,7 +2264,7 @@
         <v>0.2205882352941301</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.893939393939501</v>
+        <v>1.893939393939502</v>
       </c>
       <c r="AH16" t="n">
         <v>2.196969696969466</v>
@@ -2295,7 +2283,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.25.1</t>
         </is>
@@ -2425,7 +2413,7 @@
         <v>0.8823529411764738</v>
       </c>
       <c r="D18" t="n">
-        <v>2.460317460317425</v>
+        <v>2.460317460317426</v>
       </c>
       <c r="E18" t="n">
         <v>0.5384615384615308</v>
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>0.25.2</t>
         </is>
@@ -2591,7 +2579,7 @@
         <v>1.357142857142934</v>
       </c>
       <c r="T19" t="n">
-        <v>1.818181818181921</v>
+        <v>1.818181818181922</v>
       </c>
       <c r="U19" t="n">
         <v>1.136363636363701</v>
@@ -2649,7 +2637,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>0.125</t>
         </is>
@@ -2661,7 +2649,7 @@
         <v>1.293103448275867</v>
       </c>
       <c r="D20" t="n">
-        <v>2.205882352941145</v>
+        <v>2.205882352941146</v>
       </c>
       <c r="E20" t="n">
         <v>1.666666666666643</v>
@@ -2767,7 +2755,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>0.125.1</t>
         </is>
@@ -2854,7 +2842,7 @@
         <v>1.343283582089629</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.391304347826224</v>
+        <v>2.391304347826223</v>
       </c>
       <c r="AD21" t="n">
         <v>1.029411764705941</v>
@@ -2885,7 +2873,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>0.125.2</t>
         </is>
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>0.125.3</t>
         </is>
@@ -3121,7 +3109,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>0.062</t>
         </is>
@@ -3239,7 +3227,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>0.062.1</t>
         </is>
@@ -3357,7 +3345,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>0.062.2</t>
         </is>
@@ -3475,7 +3463,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>0.062.3</t>
         </is>
@@ -3607,29 +3595,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Vandetanib (G11)\O2_dom_freq.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Vandetanib (G11)/O2_dom_freq.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
